--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829361</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829365</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829370</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829373</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829375</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829384</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829376</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829364</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829391</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829355</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2634,6 +2724,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829357</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2746,6 +2841,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2866,6 +2966,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829366</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2986,6 +3091,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829368</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3106,6 +3216,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829372</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3226,6 +3341,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829379</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829382</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3466,6 +3591,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829383</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3586,6 +3716,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829385</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3706,6 +3841,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829386</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3826,6 +3966,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829387</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3946,6 +4091,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829388</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4066,6 +4216,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829390</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4173,6 +4328,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829378</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4280,8 +4440,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134829381</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>134829355</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134829357</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>134829358</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>134829366</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>134829368</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>134829372</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>134829379</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>134829382</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>134829383</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>134829385</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134829386</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>134829387</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>134829388</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134829390</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>134829355</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134829357</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>134829358</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>134829366</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>134829368</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>134829372</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>134829379</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>134829382</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>134829383</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>134829385</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134829386</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>134829387</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>134829388</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134829390</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>134829355</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134829357</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>134829358</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>134829366</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>134829368</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>134829372</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>134829379</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>134829382</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>134829383</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>134829385</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134829386</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>134829387</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>134829388</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134829390</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>134829355</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134829357</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>134829358</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>134829366</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>134829368</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>134829372</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>134829379</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>134829382</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>134829383</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>134829385</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134829386</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>134829387</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>134829388</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134829390</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>134829391</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>134829355</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>134829357</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>134829358</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>134829366</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>134829368</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>134829372</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>134829379</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>134829382</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>134829383</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>134829385</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134829386</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>134829387</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>134829388</v>
       </c>
       <c r="B30" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134829390</v>
       </c>
       <c r="B31" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21190-2026 artfynd.xlsx
+++ b/artfynd/A 21190-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134829356</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>134829361</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134829362</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134829365</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>134829367</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134829369</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>134829370</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>134829371</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>134829373</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134829375</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>134829377</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>134829384</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>134829376</v>
       </c>
       <c r="B14" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>134829363</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>134829364</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>134829378</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>134829381</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
